--- a/AAII_Financials/Yearly/MEOH_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/MEOH_YR_FIN.xlsx
@@ -783,7 +783,7 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>2593000</v>
+        <v>2569000</v>
       </c>
       <c r="E9" s="3">
         <v>2918100</v>
@@ -834,7 +834,7 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>996200</v>
+        <v>1020200</v>
       </c>
       <c r="E10" s="3">
         <v>801700</v>
@@ -1008,7 +1008,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>71100</v>
+        <v>101100</v>
       </c>
       <c r="E14" s="3">
         <v>65700</v>
@@ -1128,7 +1128,7 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>3087000</v>
+        <v>3063000</v>
       </c>
       <c r="E17" s="3">
         <v>3292100</v>
@@ -1179,7 +1179,7 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>502200</v>
+        <v>526200</v>
       </c>
       <c r="E18" s="3">
         <v>427700</v>
@@ -1302,7 +1302,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>914300</v>
+        <v>938300</v>
       </c>
       <c r="E21" s="3">
         <v>851700</v>
